--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487658_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487658_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1416</v>
+        <v>13.4668</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6865</v>
+        <v>12.8481</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4552</v>
+        <v>0.6187</v>
       </c>
       <c r="G2" t="n">
         <v>10.443</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4372</v>
+        <v>0.888</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8479</v>
+        <v>0.3137</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4107</v>
+        <v>0.5743</v>
       </c>
       <c r="V2" t="n">
         <v>1.5537</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9973</v>
+        <v>5.2653</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7175</v>
+        <v>3.2581</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2798</v>
+        <v>2.0072</v>
       </c>
       <c r="G3" t="n">
         <v>1.0171</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0563</v>
+        <v>1.3243</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1253</v>
+        <v>0.6659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.931</v>
+        <v>0.6584</v>
       </c>
       <c r="V3" t="n">
         <v>2.7298</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7546</v>
+        <v>2.6514</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6172</v>
+        <v>0.7593</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1374</v>
+        <v>1.8921</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1963</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6792</v>
+        <v>1.5761</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7301</v>
+        <v>0.8723</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.7038</v>
       </c>
       <c r="V4" t="n">
         <v>1.8836</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7053</v>
+        <v>2.1681</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0662</v>
+        <v>2.3655</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3609</v>
+        <v>-0.1974</v>
       </c>
       <c r="G5" t="n">
         <v>1.1282</v>
@@ -844,13 +844,13 @@
         <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5771</v>
+        <v>1.04</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6386</v>
+        <v>0.9379</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0614</v>
+        <v>0.1021</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0205</v>
+        <v>1.9179</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5692</v>
+        <v>1.412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4513</v>
+        <v>0.5058</v>
       </c>
       <c r="G6" t="n">
         <v>0.5985</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8004</v>
+        <v>0.097</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9085</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1081</v>
+        <v>0.1626</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3299</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4847</v>
+        <v>1.0697</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4107</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.074</v>
+        <v>0.2375</v>
       </c>
       <c r="G7" t="n">
         <v>0.5574</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4607</v>
+        <v>0.1242</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>0.1186</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1579</v>
+        <v>0.0056</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0382</v>
+        <v>0.745</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.069</v>
+        <v>-0.3077</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1072</v>
+        <v>1.0527</v>
       </c>
       <c r="G8" t="n">
         <v>0.3415</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1092</v>
+        <v>0.5975</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5451</v>
+        <v>0.2162</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4359</v>
+        <v>0.3813</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0067</v>
+        <v>-0.163</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6226</v>
+        <v>-0.6015</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6293</v>
+        <v>0.4385</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0415</v>
@@ -1156,13 +1156,13 @@
         <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2721</v>
+        <v>0.1024</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0617</v>
+        <v>0.0827</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2104</v>
+        <v>0.0197</v>
       </c>
       <c r="V9" t="n">
         <v>0.6119</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3517</v>
+        <v>-0.6846</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0522</v>
+        <v>0.9164</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4039</v>
+        <v>-1.601</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7357</v>
+        <v>-2.8192</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0412</v>
+        <v>-2.1585</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7769</v>
+        <v>-0.6607</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4443</v>
+        <v>-0.3978</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4037</v>
+        <v>-0.5602</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>0.1624</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.18</v>
+        <v>-2.4214</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3625</v>
+        <v>-1.5983</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8175</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8317</v>
+        <v>1.4465</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6079</v>
+        <v>0.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2239</v>
+        <v>0.6965</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2239</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. RODRÍGUEZ MACHÍN</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6996</v>
+        <v>-0.7099</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9559</v>
+        <v>0.6122</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6555</v>
+        <v>-1.3221</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8192</v>
+        <v>-0.7357</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1585</v>
+        <v>0.0412</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6607</v>
+        <v>-0.7769</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3978</v>
+        <v>0.4443</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5602</v>
+        <v>0.4037</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1624</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4214</v>
+        <v>-1.18</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5983</v>
+        <v>-0.3625</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8175</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4316</v>
+        <v>0.4736</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7896</v>
+        <v>0.1679</v>
       </c>
       <c r="U11" t="n">
-        <v>0.642</v>
+        <v>0.3056</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8462</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2474</v>
+        <v>-2.565</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7591</v>
+        <v>-1.1585</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4883</v>
+        <v>-1.4066</v>
       </c>
       <c r="G12" t="n">
         <v>-3.088</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1878</v>
+        <v>0.4946</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5451</v>
+        <v>0.0555</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3573</v>
+        <v>0.4391</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.8502</v>
+        <v>23.1617</v>
       </c>
       <c r="E13" t="n">
-        <v>19.6247</v>
+        <v>20.9361</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2256</v>
+        <v>2.2254</v>
       </c>
       <c r="G13" t="n">
         <v>4.204999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>13.5825</v>
       </c>
       <c r="S13" t="n">
-        <v>6.8527</v>
+        <v>8.164199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8038</v>
+        <v>4.115100000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.0491</v>
+        <v>4.048999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>4.0013</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0395</v>
+        <v>2.3581</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7116</v>
+        <v>4.112</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6721</v>
+        <v>-1.7538</v>
       </c>
       <c r="G14" t="n">
         <v>2.749</v>
@@ -1546,13 +1546,13 @@
         <v>1.3582</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9035</v>
+        <v>-0.5849</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9444</v>
+        <v>-0.544</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0409</v>
+        <v>-0.0409</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5654</v>
+        <v>-0.4108</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5967</v>
+        <v>3.6968</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.162</v>
+        <v>-4.1075</v>
       </c>
       <c r="G15" t="n">
         <v>0.008699999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1279</v>
+        <v>-0.9732</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5799</v>
+        <v>-0.4798</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.548</v>
+        <v>-0.4935</v>
       </c>
       <c r="V15" t="n">
         <v>0.9418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4357</v>
+        <v>-1.3717</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9044</v>
+        <v>-0.7042</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5312</v>
+        <v>-0.6675</v>
       </c>
       <c r="G16" t="n">
         <v>0.5663</v>
@@ -1702,13 +1702,13 @@
         <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0498</v>
+        <v>-0.9859</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7874</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2624</v>
+        <v>-0.3987</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4636</v>
+        <v>-2.0003</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9659</v>
+        <v>0.5655</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4295</v>
+        <v>-2.5657</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8895999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6976</v>
+        <v>0.1609</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2691</v>
+        <v>-0.1313</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4285</v>
+        <v>0.2922</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2716</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6885</v>
+        <v>-2.4704</v>
       </c>
       <c r="E18" t="n">
         <v>0.1679</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8564</v>
+        <v>-2.6383</v>
       </c>
       <c r="G18" t="n">
         <v>1.8221</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1225</v>
+        <v>-1.9044</v>
       </c>
       <c r="T18" t="n">
         <v>-0.9691</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1534</v>
+        <v>-0.9354</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0258</v>
+        <v>-3.7077</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.7048</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2209</v>
+        <v>-3.0029</v>
       </c>
       <c r="G19" t="n">
         <v>-2.5499</v>
@@ -1936,13 +1936,13 @@
         <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3997</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1559</v>
+        <v>-0.0558</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2438</v>
+        <v>-0.0258</v>
       </c>
       <c r="V19" t="n">
         <v>0.2821</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.059</v>
+        <v>-6.5679</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1786</v>
+        <v>-2.2787</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8804</v>
+        <v>-4.2892</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2582</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5888</v>
+        <v>-1.0977</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5193</v>
+        <v>-0.6194</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.4783</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8836</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.6519</v>
+        <v>-7.6796</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.7796</v>
+        <v>-7.0799</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8723</v>
+        <v>-0.5997</v>
       </c>
       <c r="G21" t="n">
         <v>-4.6533</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3582</v>
+        <v>-1.386</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3623</v>
+        <v>-0.6626</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9959</v>
+        <v>-0.7234</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-21.8504</v>
+        <v>-21.8503</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.225400000000001</v>
+        <v>-2.2254</v>
       </c>
       <c r="F22" t="n">
-        <v>-19.6248</v>
+        <v>-19.6246</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2049</v>
@@ -2170,13 +2170,13 @@
         <v>6.7911</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.8528</v>
+        <v>-6.852799999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-4.0492</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8036</v>
+        <v>-2.8038</v>
       </c>
       <c r="V22" t="n">
         <v>-4.0015</v>
